--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121255774</v>
       </c>
       <c r="B2" t="n">
-        <v>78243</v>
+        <v>78246</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121255640</v>
       </c>
       <c r="B3" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B2" t="n">
-        <v>78246</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R2" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78246</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R3" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121255640</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>79685</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>121255774</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
+        <v>78249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B2" t="n">
-        <v>79685</v>
+        <v>78249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R2" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B3" t="n">
-        <v>78249</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R3" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B2" t="n">
-        <v>78249</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R2" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>78252</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R3" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>78252</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R2" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B3" t="n">
-        <v>78252</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R3" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121255774</v>
       </c>
       <c r="B2" t="n">
-        <v>78252</v>
+        <v>78253</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121255640</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B2" t="n">
-        <v>78253</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R2" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>78254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R3" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>78254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R2" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B3" t="n">
-        <v>78254</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R3" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121255774</v>
+        <v>121255640</v>
       </c>
       <c r="B2" t="n">
-        <v>78254</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>466460</v>
+        <v>466414</v>
       </c>
       <c r="R2" t="n">
-        <v>6873806</v>
+        <v>6873784</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-19</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121255640</v>
+        <v>121255774</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>78254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +822,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466414</v>
+        <v>466460</v>
       </c>
       <c r="R3" t="n">
-        <v>6873784</v>
+        <v>6873806</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Inom avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,6 +882,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125153460</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78455</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>353</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tällberget, Tällberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>466281</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6873910</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>125153460</v>
       </c>
       <c r="B4" t="n">
-        <v>78455</v>
+        <v>78592</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 34191-2020 artfynd.xlsx
+++ b/artfynd/A 34191-2020 artfynd.xlsx
@@ -887,12 +887,7 @@
         <v>125153460</v>
       </c>
       <c r="B4" t="n">
-        <v>78592</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
